--- a/backend/assets/report-templates/employee-leave-report.xlsx
+++ b/backend/assets/report-templates/employee-leave-report.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="請假表" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">請假表!$A1:$R39</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -17,68 +20,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <authors>
-    <author>作者不明</author>
-  </authors>
-  <commentList>
-    <comment ref="A5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK TC"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">真實請假日開始日
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK TC"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">真實請假日開始日
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK TC"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">真實請假結束日
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Noto Sans CJK TC"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">真實請假結束日
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -189,7 +130,7 @@
     <numFmt numFmtId="168" formatCode="General"/>
     <numFmt numFmtId="169" formatCode="mm\月dd\日;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,11 +175,6 @@
       <name val="微軟正黑體"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Noto Sans CJK TC"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -380,7 +316,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -745,14 +681,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="24.95" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:R40"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="24.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="7.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="3" style="1" width="6.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="8.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="7.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="7.24"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16365" style="2" width="10.49"/>
   </cols>
   <sheetData>
@@ -776,7 +712,7 @@
       <c r="Q1" s="3"/>
       <c r="R1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="20.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
         <v>0</v>
@@ -807,9 +743,8 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="9"/>
       <c r="R2" s="10"/>
-      <c r="S2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" customFormat="false" ht="20.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="11" t="s">
         <v>5</v>
@@ -843,7 +778,6 @@
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="12"/>
-      <c r="S3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13"/>
@@ -865,7 +799,7 @@
       <c r="Q4" s="13"/>
       <c r="R4" s="14"/>
     </row>
-    <row r="5" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
@@ -920,9 +854,8 @@
       <c r="R5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
         <v>28</v>
       </c>
@@ -976,7 +909,7 @@
       </c>
       <c r="R6" s="22"/>
     </row>
-    <row r="7" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="n">
         <v>46136</v>
       </c>
@@ -1032,7 +965,7 @@
       </c>
       <c r="R7" s="22"/>
     </row>
-    <row r="8" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="n">
         <v>46140</v>
       </c>
@@ -1088,7 +1021,7 @@
       </c>
       <c r="R8" s="22"/>
     </row>
-    <row r="9" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="n">
         <v>46174</v>
       </c>
@@ -1144,7 +1077,7 @@
       </c>
       <c r="R9" s="22"/>
     </row>
-    <row r="10" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="n">
         <v>46216</v>
       </c>
@@ -1200,7 +1133,7 @@
       </c>
       <c r="R10" s="22"/>
     </row>
-    <row r="11" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="n">
         <v>46206</v>
       </c>
@@ -1256,7 +1189,7 @@
       </c>
       <c r="R11" s="22"/>
     </row>
-    <row r="12" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="n">
         <v>46212</v>
       </c>
@@ -1312,7 +1245,7 @@
       </c>
       <c r="R12" s="22"/>
     </row>
-    <row r="13" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="23"/>
       <c r="B13" s="24"/>
       <c r="C13" s="19" t="n">
@@ -1364,7 +1297,7 @@
       </c>
       <c r="R13" s="22"/>
     </row>
-    <row r="14" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="23"/>
       <c r="B14" s="24"/>
       <c r="C14" s="19" t="n">
@@ -1416,7 +1349,7 @@
       </c>
       <c r="R14" s="22"/>
     </row>
-    <row r="15" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="23"/>
       <c r="B15" s="24"/>
       <c r="C15" s="19" t="n">
@@ -1468,7 +1401,7 @@
       </c>
       <c r="R15" s="22"/>
     </row>
-    <row r="16" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="19" t="n">
@@ -1520,7 +1453,7 @@
       </c>
       <c r="R16" s="22"/>
     </row>
-    <row r="17" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="19" t="n">
@@ -1572,45 +1505,21 @@
       </c>
       <c r="R17" s="22"/>
     </row>
-    <row r="18" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="23"/>
       <c r="B18" s="24"/>
-      <c r="C18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
       <c r="O18" s="20" t="n">
         <v>0</v>
       </c>
@@ -1624,320 +1533,344 @@
       </c>
       <c r="R18" s="22"/>
     </row>
-    <row r="19" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="21" t="n">
-        <f aca="false">P18+O19</f>
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="26" t="n">
+        <f aca="false">SUM(C6:C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <f aca="false">SUM(D6:D18)</f>
+        <v>48</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <f aca="false">SUM(E6:E18)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <f aca="false">SUM(F6:F18)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <f aca="false">SUM(G6:G18)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <f aca="false">SUM(H6:H18)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="26" t="n">
+        <f aca="false">SUM(I6:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="26" t="n">
+        <f aca="false">SUM(J6:J18)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <f aca="false">SUM(K6:K18)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="26" t="n">
+        <f aca="false">SUM(L6:L18)</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="26" t="n">
+        <f aca="false">SUM(M6:M18)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="26" t="n">
+        <f aca="false">SUM(N6:N18)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="27" t="n">
+        <f aca="false">SUM(O6:O18)</f>
         <v>56</v>
       </c>
-      <c r="Q19" s="21" t="n">
-        <f aca="false">L3-P19</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="22"/>
-    </row>
-    <row r="20" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <f aca="false">P19+O20</f>
+      <c r="P19" s="28" t="n">
+        <f aca="false">P18</f>
         <v>56</v>
       </c>
-      <c r="Q20" s="21" t="n">
-        <f aca="false">L3-P20</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="22"/>
-    </row>
-    <row r="21" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26" t="n">
-        <f aca="false">SUM(C6:C19)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="26" t="n">
-        <f aca="false">SUM(D6:D19)</f>
-        <v>48</v>
-      </c>
-      <c r="E21" s="26" t="n">
-        <f aca="false">SUM(E6:E19)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="26" t="n">
-        <f aca="false">SUM(F6:F19)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="26" t="n">
-        <f aca="false">SUM(G6:G19)</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="26" t="n">
-        <f aca="false">SUM(H6:H19)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="26" t="n">
-        <f aca="false">SUM(I6:I19)</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="26" t="n">
-        <f aca="false">SUM(J6:J19)</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="26" t="n">
-        <f aca="false">SUM(K6:K19)</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="26" t="n">
-        <f aca="false">SUM(L6:L19)</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="26" t="n">
-        <f aca="false">SUM(M6:M19)</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="26" t="n">
-        <f aca="false">SUM(N6:N19)</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="27" t="n">
-        <f aca="false">SUM(O6:O20)</f>
-        <v>56</v>
-      </c>
-      <c r="P21" s="28" t="n">
-        <f aca="false">P20</f>
-        <v>56</v>
-      </c>
-      <c r="Q21" s="28" t="n">
-        <f aca="false">Q20</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="29"/>
-    </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7" t="s">
+      <c r="Q19" s="28" t="n">
+        <f aca="false">Q18</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="29"/>
+    </row>
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="20.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="6" t="s">
+      <c r="E22" s="7"/>
+      <c r="F22" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="8" t="n">
+      <c r="G22" s="6"/>
+      <c r="H22" s="8" t="n">
         <v>5006</v>
       </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="6" t="s">
+      <c r="I22" s="8"/>
+      <c r="J22" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="8" t="s">
+      <c r="K22" s="6"/>
+      <c r="L22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="10"/>
-    </row>
-    <row r="25" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="11" t="s">
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="20.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5"/>
+      <c r="B23" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="7" t="s">
+      <c r="C23" s="11"/>
+      <c r="D23" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="6" t="s">
+      <c r="E23" s="7"/>
+      <c r="F23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="8" t="n">
+      <c r="G23" s="6"/>
+      <c r="H23" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="11" t="s">
+      <c r="I23" s="8"/>
+      <c r="J23" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="8" t="n">
+      <c r="K23" s="11"/>
+      <c r="L23" s="8" t="n">
         <f aca="false">H25*8</f>
         <v>112</v>
       </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="6" t="s">
+      <c r="M23" s="8"/>
+      <c r="N23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="O25" s="6"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="12"/>
-    </row>
-    <row r="26" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="14"/>
-    </row>
-    <row r="27" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
+      <c r="O23" s="6"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="11.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B25" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C25" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D25" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E25" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G25" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H25" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="16" t="s">
+      <c r="I25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="16" t="s">
+      <c r="J25" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="16" t="s">
+      <c r="L25" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M25" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="N27" s="16" t="s">
+      <c r="N25" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="O27" s="16" t="s">
+      <c r="O25" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P27" s="16" t="s">
+      <c r="P25" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="Q27" s="16" t="s">
+      <c r="Q25" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="R27" s="17" t="s">
+      <c r="R25" s="17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="30"/>
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="20" t="n">
+        <f aca="false">O26</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="21" t="n">
+        <f aca="false">L23-P26</f>
+        <v>112</v>
+      </c>
+      <c r="R26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="21" t="n">
+        <f aca="false">P26+O27</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="21" t="n">
+        <f aca="false">L23-P27</f>
+        <v>112</v>
+      </c>
+      <c r="R27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23"/>
+      <c r="B28" s="24"/>
       <c r="C28" s="19" t="n">
         <v>0</v>
       </c>
@@ -1977,17 +1910,17 @@
       <c r="O28" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="P28" s="20" t="n">
-        <f aca="false">O28</f>
+      <c r="P28" s="21" t="n">
+        <f aca="false">P27+O28</f>
         <v>0</v>
       </c>
       <c r="Q28" s="21" t="n">
-        <f aca="false">L25-P28</f>
+        <f aca="false">L23-P28</f>
         <v>112</v>
       </c>
       <c r="R28" s="22"/>
     </row>
-    <row r="29" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="23"/>
       <c r="B29" s="24"/>
       <c r="C29" s="19" t="n">
@@ -2034,12 +1967,12 @@
         <v>0</v>
       </c>
       <c r="Q29" s="21" t="n">
-        <f aca="false">L25-P29</f>
+        <f aca="false">L23-P29</f>
         <v>112</v>
       </c>
       <c r="R29" s="22"/>
     </row>
-    <row r="30" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="23"/>
       <c r="B30" s="24"/>
       <c r="C30" s="19" t="n">
@@ -2086,12 +2019,12 @@
         <v>0</v>
       </c>
       <c r="Q30" s="21" t="n">
-        <f aca="false">L25-P30</f>
+        <f aca="false">L23-P30</f>
         <v>112</v>
       </c>
       <c r="R30" s="22"/>
     </row>
-    <row r="31" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="23"/>
       <c r="B31" s="24"/>
       <c r="C31" s="19" t="n">
@@ -2138,12 +2071,12 @@
         <v>0</v>
       </c>
       <c r="Q31" s="21" t="n">
-        <f aca="false">L25-P31</f>
+        <f aca="false">L23-P31</f>
         <v>112</v>
       </c>
       <c r="R31" s="22"/>
     </row>
-    <row r="32" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="23"/>
       <c r="B32" s="24"/>
       <c r="C32" s="19" t="n">
@@ -2190,12 +2123,12 @@
         <v>0</v>
       </c>
       <c r="Q32" s="21" t="n">
-        <f aca="false">L25-P32</f>
+        <f aca="false">L23-P32</f>
         <v>112</v>
       </c>
       <c r="R32" s="22"/>
     </row>
-    <row r="33" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="23"/>
       <c r="B33" s="24"/>
       <c r="C33" s="19" t="n">
@@ -2242,12 +2175,12 @@
         <v>0</v>
       </c>
       <c r="Q33" s="21" t="n">
-        <f aca="false">L25-P33</f>
+        <f aca="false">L23-P33</f>
         <v>112</v>
       </c>
       <c r="R33" s="22"/>
     </row>
-    <row r="34" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="23"/>
       <c r="B34" s="24"/>
       <c r="C34" s="19" t="n">
@@ -2294,12 +2227,12 @@
         <v>0</v>
       </c>
       <c r="Q34" s="21" t="n">
-        <f aca="false">L25-P34</f>
+        <f aca="false">L23-P34</f>
         <v>112</v>
       </c>
       <c r="R34" s="22"/>
     </row>
-    <row r="35" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="23"/>
       <c r="B35" s="24"/>
       <c r="C35" s="19" t="n">
@@ -2346,12 +2279,12 @@
         <v>0</v>
       </c>
       <c r="Q35" s="21" t="n">
-        <f aca="false">L25-P35</f>
+        <f aca="false">L23-P35</f>
         <v>112</v>
       </c>
       <c r="R35" s="22"/>
     </row>
-    <row r="36" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="23"/>
       <c r="B36" s="24"/>
       <c r="C36" s="19" t="n">
@@ -2398,12 +2331,12 @@
         <v>0</v>
       </c>
       <c r="Q36" s="21" t="n">
-        <f aca="false">L25-P36</f>
+        <f aca="false">L23-P36</f>
         <v>112</v>
       </c>
       <c r="R36" s="22"/>
     </row>
-    <row r="37" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="23"/>
       <c r="B37" s="24"/>
       <c r="C37" s="19" t="n">
@@ -2450,50 +2383,26 @@
         <v>0</v>
       </c>
       <c r="Q37" s="21" t="n">
-        <f aca="false">L25-P37</f>
+        <f aca="false">L23-P37</f>
         <v>112</v>
       </c>
       <c r="R37" s="22"/>
     </row>
-    <row r="38" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="23"/>
       <c r="B38" s="24"/>
-      <c r="C38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
       <c r="O38" s="20" t="n">
         <v>0</v>
       </c>
@@ -2502,263 +2411,79 @@
         <v>0</v>
       </c>
       <c r="Q38" s="21" t="n">
-        <f aca="false">L25-P38</f>
+        <f aca="false">L23-P38</f>
         <v>112</v>
       </c>
       <c r="R38" s="22"/>
     </row>
-    <row r="39" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="21" t="n">
-        <f aca="false">P38+O39</f>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="21" t="n">
-        <f aca="false">L25-P39</f>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="26" t="n">
+        <f aca="false">SUM(C26:C38)</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="26" t="n">
+        <f aca="false">SUM(D26:D38)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="26" t="n">
+        <f aca="false">SUM(E26:E38)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="26" t="n">
+        <f aca="false">SUM(F26:F38)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="26" t="n">
+        <f aca="false">SUM(G26:G38)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <f aca="false">SUM(H26:H38)</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <f aca="false">SUM(I26:I38)</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="26" t="n">
+        <f aca="false">SUM(J26:J38)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="26" t="n">
+        <f aca="false">SUM(K26:K38)</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="26" t="n">
+        <f aca="false">SUM(L26:L38)</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="26" t="n">
+        <f aca="false">SUM(M26:M38)</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="26" t="n">
+        <f aca="false">SUM(N26:N38)</f>
+        <v>0</v>
+      </c>
+      <c r="O39" s="27" t="n">
+        <f aca="false">SUM(O26:O38)</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="28" t="n">
+        <f aca="false">P38</f>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="28" t="n">
+        <f aca="false">Q38</f>
         <v>112</v>
       </c>
-      <c r="R39" s="22"/>
-    </row>
-    <row r="40" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="21" t="n">
-        <f aca="false">P39+O40</f>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="21" t="n">
-        <f aca="false">L25-P40</f>
-        <v>112</v>
-      </c>
-      <c r="R40" s="22"/>
-    </row>
-    <row r="41" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="21" t="n">
-        <f aca="false">P40+O41</f>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="21" t="n">
-        <f aca="false">L25-P41</f>
-        <v>112</v>
-      </c>
-      <c r="R41" s="22"/>
-    </row>
-    <row r="42" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="21" t="n">
-        <f aca="false">P41+O42</f>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="21" t="n">
-        <f aca="false">L25-P42</f>
-        <v>112</v>
-      </c>
-      <c r="R42" s="22"/>
-    </row>
-    <row r="43" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="26" t="n">
-        <f aca="false">SUM(C28:C41)</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="26" t="n">
-        <f aca="false">SUM(D28:D41)</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="26" t="n">
-        <f aca="false">SUM(E28:E41)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="26" t="n">
-        <f aca="false">SUM(F28:F41)</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="26" t="n">
-        <f aca="false">SUM(G28:G41)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="26" t="n">
-        <f aca="false">SUM(H28:H41)</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="26" t="n">
-        <f aca="false">SUM(I28:I41)</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="26" t="n">
-        <f aca="false">SUM(J28:J41)</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="26" t="n">
-        <f aca="false">SUM(K28:K41)</f>
-        <v>0</v>
-      </c>
-      <c r="L43" s="26" t="n">
-        <f aca="false">SUM(L28:L41)</f>
-        <v>0</v>
-      </c>
-      <c r="M43" s="26" t="n">
-        <f aca="false">SUM(M28:M41)</f>
-        <v>0</v>
-      </c>
-      <c r="N43" s="26" t="n">
-        <f aca="false">SUM(N28:N41)</f>
-        <v>0</v>
-      </c>
-      <c r="O43" s="27" t="n">
-        <f aca="false">SUM(O28:O42)</f>
-        <v>0</v>
-      </c>
-      <c r="P43" s="28" t="n">
-        <f aca="false">P42</f>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="28" t="n">
-        <f aca="false">Q42</f>
-        <v>112</v>
-      </c>
-      <c r="R43" s="29"/>
-    </row>
-    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="R39" s="29"/>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="37">
     <mergeCell ref="A1:Q1"/>
@@ -2779,33 +2504,32 @@
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="A26:Q26"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A21:Q21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="A24:Q24"/>
+    <mergeCell ref="A39:B39"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.39375" top="0.472222222222222" bottom="0.472222222222222" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/backend/assets/report-templates/employee-leave-report.xlsx
+++ b/backend/assets/report-templates/employee-leave-report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="30">
   <si>
     <t xml:space="preserve">卡號：</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t xml:space="preserve">林協志</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特休期間：</t>
   </si>
 </sst>
 </file>
@@ -687,7 +690,7 @@
   <dimension ref="A1:R59"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -707,7 +710,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -727,7 +730,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -747,7 +750,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -767,7 +770,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -787,7 +790,7 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -807,7 +810,7 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -827,7 +830,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -847,7 +850,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -867,7 +870,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -887,7 +890,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -907,7 +910,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -927,7 +930,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -947,7 +950,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -967,7 +970,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -987,7 +990,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1007,7 +1010,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1027,7 +1030,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1047,7 +1050,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1067,7 +1070,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1087,7 +1090,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1107,7 +1110,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
         <v>0</v>
@@ -1133,7 +1136,7 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="9" t="s">
         <v>3</v>
@@ -1165,7 +1168,7 @@
       <c r="Q23" s="6"/>
       <c r="R23" s="10"/>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1241,7 +1244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17"/>
       <c r="B26" s="18"/>
       <c r="C26" s="19" t="n">
@@ -1293,7 +1296,7 @@
       </c>
       <c r="R26" s="22"/>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="n">
         <v>46136</v>
       </c>
@@ -1349,7 +1352,7 @@
       </c>
       <c r="R27" s="22"/>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="n">
         <v>46140</v>
       </c>
@@ -1405,7 +1408,7 @@
       </c>
       <c r="R28" s="22"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="n">
         <v>46174</v>
       </c>
@@ -1461,7 +1464,7 @@
       </c>
       <c r="R29" s="22"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="n">
         <v>46216</v>
       </c>
@@ -1517,7 +1520,7 @@
       </c>
       <c r="R30" s="22"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="n">
         <v>46206</v>
       </c>
@@ -1573,7 +1576,7 @@
       </c>
       <c r="R31" s="22"/>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="n">
         <v>46212</v>
       </c>
@@ -1629,7 +1632,7 @@
       </c>
       <c r="R32" s="22"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17"/>
       <c r="B33" s="18"/>
       <c r="C33" s="19" t="n">
@@ -1681,7 +1684,7 @@
       </c>
       <c r="R33" s="22"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17"/>
       <c r="B34" s="18"/>
       <c r="C34" s="19" t="n">
@@ -1733,7 +1736,7 @@
       </c>
       <c r="R34" s="22"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17"/>
       <c r="B35" s="18"/>
       <c r="C35" s="19" t="n">
@@ -1785,7 +1788,7 @@
       </c>
       <c r="R35" s="22"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17"/>
       <c r="B36" s="18"/>
       <c r="C36" s="19" t="n">
@@ -1837,7 +1840,7 @@
       </c>
       <c r="R36" s="22"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17"/>
       <c r="B37" s="18"/>
       <c r="C37" s="19" t="n">
@@ -1889,7 +1892,7 @@
       </c>
       <c r="R37" s="22"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17"/>
       <c r="B38" s="18"/>
       <c r="C38" s="19"/>
@@ -1917,7 +1920,7 @@
       </c>
       <c r="R38" s="22"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
         <v>25</v>
       </c>
@@ -1984,7 +1987,7 @@
       </c>
       <c r="R39" s="27"/>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28"/>
       <c r="B40" s="28"/>
       <c r="C40" s="28"/>
@@ -2004,7 +2007,7 @@
       <c r="Q40" s="28"/>
       <c r="R40" s="28"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2024,7 +2027,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
         <v>0</v>
@@ -2056,7 +2059,7 @@
       <c r="Q42" s="7"/>
       <c r="R42" s="8"/>
     </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="9" t="s">
         <v>3</v>
@@ -2090,7 +2093,7 @@
       <c r="Q43" s="6"/>
       <c r="R43" s="10"/>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
@@ -2166,7 +2169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="17"/>
       <c r="B46" s="18"/>
       <c r="C46" s="19" t="n">
@@ -2218,7 +2221,7 @@
       </c>
       <c r="R46" s="22"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17"/>
       <c r="B47" s="18"/>
       <c r="C47" s="19" t="n">
@@ -2270,7 +2273,7 @@
       </c>
       <c r="R47" s="22"/>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="17"/>
       <c r="B48" s="18"/>
       <c r="C48" s="19" t="n">
@@ -2322,7 +2325,7 @@
       </c>
       <c r="R48" s="22"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17"/>
       <c r="B49" s="18"/>
       <c r="C49" s="19" t="n">
@@ -2374,7 +2377,7 @@
       </c>
       <c r="R49" s="22"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17"/>
       <c r="B50" s="18"/>
       <c r="C50" s="19" t="n">
@@ -2426,7 +2429,7 @@
       </c>
       <c r="R50" s="22"/>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17"/>
       <c r="B51" s="18"/>
       <c r="C51" s="19" t="n">
@@ -2478,7 +2481,7 @@
       </c>
       <c r="R51" s="22"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17"/>
       <c r="B52" s="18"/>
       <c r="C52" s="19" t="n">
@@ -2530,7 +2533,7 @@
       </c>
       <c r="R52" s="22"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17"/>
       <c r="B53" s="18"/>
       <c r="C53" s="19" t="n">
@@ -2582,7 +2585,7 @@
       </c>
       <c r="R53" s="22"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="17"/>
       <c r="B54" s="18"/>
       <c r="C54" s="19" t="n">
@@ -2634,7 +2637,7 @@
       </c>
       <c r="R54" s="22"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17"/>
       <c r="B55" s="18"/>
       <c r="C55" s="19" t="n">
@@ -2686,7 +2689,7 @@
       </c>
       <c r="R55" s="22"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17"/>
       <c r="B56" s="18"/>
       <c r="C56" s="19" t="n">
@@ -2738,7 +2741,7 @@
       </c>
       <c r="R56" s="22"/>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="17"/>
       <c r="B57" s="18"/>
       <c r="C57" s="19" t="n">
@@ -2790,7 +2793,7 @@
       </c>
       <c r="R57" s="22"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="17"/>
       <c r="B58" s="18"/>
       <c r="C58" s="19"/>
@@ -2818,7 +2821,7 @@
       </c>
       <c r="R58" s="22"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="23" t="s">
         <v>25</v>
       </c>
@@ -2985,7 +2988,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="4" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="6"/>
@@ -3859,7 +3862,7 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="4" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="6"/>
